--- a/excel-files/VALENZUELA/BAGBAGUIN NATIONAL HIGH SCHOOL.xlsx
+++ b/excel-files/VALENZUELA/BAGBAGUIN NATIONAL HIGH SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29704"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29922"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E6BEA86-3424-41E6-9F0F-E68DAE6FF60A}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF816DA6-7F49-4520-AAB8-EFE714CCBDA7}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -5528,12 +5528,15 @@
     <protectedRange sqref="F1:F98" name="SOURCE"/>
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E91:E98 E8:E12 E41:E49 E2:E6" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
       <formula1>"2024,2025"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E51:E59 E61:E69 E71:E79 E81:E89" xr:uid="{152A15A2-22A8-4AE2-BE9D-2EA56129AF04}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5545,7 +5548,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -9441,7 +9444,7 @@
       <c r="Z62" s="13"/>
       <c r="AA62" s="13"/>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    <row r="63" spans="1:27" ht="19.5">
       <c r="A63" s="10">
         <v>7</v>
       </c>
@@ -9510,7 +9513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
+    <row r="64" spans="1:27" ht="19.5">
       <c r="A64" s="10">
         <v>7</v>
       </c>
@@ -9579,7 +9582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+    <row r="65" spans="1:27" ht="19.5">
       <c r="A65" s="10">
         <v>7</v>
       </c>
@@ -9648,7 +9651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="19.149999999999999">
+    <row r="66" spans="1:27" ht="19.5">
       <c r="A66" s="10">
         <v>7</v>
       </c>
@@ -9717,7 +9720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="67" spans="1:27" ht="38.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -9786,7 +9789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="19.5">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -9855,7 +9858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="19.5">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -9924,7 +9927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="19.5">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -9993,7 +9996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="19.5">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -10062,21 +10065,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.5" hidden="1">
       <c r="J72" s="13"/>
+      <c r="L72" s="10"/>
       <c r="M72" s="5"/>
       <c r="N72" s="13"/>
       <c r="O72" s="13"/>
       <c r="P72" s="13"/>
+      <c r="R72" s="10"/>
       <c r="S72" s="5"/>
       <c r="T72" s="13"/>
       <c r="U72" s="13"/>
       <c r="V72" s="13"/>
+      <c r="X72" s="10"/>
       <c r="Y72" s="5"/>
       <c r="Z72" s="13"/>
       <c r="AA72" s="13"/>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="19.5">
       <c r="A73" s="10">
         <v>8</v>
       </c>
@@ -10145,7 +10151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="19.5">
       <c r="A74" s="10">
         <v>8</v>
       </c>
@@ -10214,7 +10220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="19.5">
       <c r="A75" s="10">
         <v>8</v>
       </c>
@@ -10283,7 +10289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="19.5">
       <c r="A76" s="10">
         <v>8</v>
       </c>
@@ -10352,7 +10358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="19.5">
       <c r="A77" s="10">
         <v>8</v>
       </c>
@@ -10421,7 +10427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" ht="19.5">
       <c r="A78" s="10">
         <v>8</v>
       </c>
@@ -10490,7 +10496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="79" spans="1:27" ht="19.5">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -10559,7 +10565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="19.5">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -10628,7 +10634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="19.5">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -10697,21 +10703,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.5" hidden="1">
       <c r="J82" s="13"/>
+      <c r="L82" s="10"/>
       <c r="M82" s="5"/>
       <c r="N82" s="13"/>
       <c r="O82" s="13"/>
       <c r="P82" s="13"/>
+      <c r="R82" s="10"/>
       <c r="S82" s="5"/>
       <c r="T82" s="13"/>
       <c r="U82" s="13"/>
       <c r="V82" s="13"/>
+      <c r="X82" s="10"/>
       <c r="Y82" s="5"/>
       <c r="Z82" s="13"/>
       <c r="AA82" s="13"/>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="19.5">
       <c r="A83" s="10">
         <v>9</v>
       </c>
@@ -10780,7 +10789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="19.5">
       <c r="A84" s="10">
         <v>9</v>
       </c>
@@ -10849,7 +10858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="19.5">
       <c r="A85" s="10">
         <v>9</v>
       </c>
@@ -10918,7 +10927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="19.5">
       <c r="A86" s="10">
         <v>9</v>
       </c>
@@ -10987,7 +10996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="19.5">
       <c r="A87" s="10">
         <v>9</v>
       </c>
@@ -11056,7 +11065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="19.5">
       <c r="A88" s="10">
         <v>9</v>
       </c>
@@ -11125,7 +11134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="19.5">
       <c r="A89" s="10">
         <v>9</v>
       </c>
@@ -11194,7 +11203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="19.149999999999999">
+    <row r="90" spans="1:27" ht="19.5">
       <c r="A90" s="10">
         <v>9</v>
       </c>
@@ -11263,7 +11272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="91" spans="1:27" ht="19.5">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -11332,21 +11341,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.5" hidden="1">
       <c r="J92" s="13"/>
+      <c r="L92" s="10"/>
       <c r="M92" s="5"/>
       <c r="N92" s="13"/>
       <c r="O92" s="13"/>
       <c r="P92" s="13"/>
+      <c r="R92" s="10"/>
       <c r="S92" s="5"/>
       <c r="T92" s="13"/>
       <c r="U92" s="13"/>
       <c r="V92" s="13"/>
+      <c r="X92" s="10"/>
       <c r="Y92" s="5"/>
       <c r="Z92" s="13"/>
       <c r="AA92" s="13"/>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="19.5">
       <c r="A93" s="10">
         <v>10</v>
       </c>
@@ -11415,7 +11427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="19.5">
       <c r="A94" s="10">
         <v>10</v>
       </c>
@@ -11484,7 +11496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="19.5">
       <c r="A95" s="10">
         <v>10</v>
       </c>
@@ -11553,7 +11565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="19.5">
       <c r="A96" s="10">
         <v>10</v>
       </c>
@@ -11622,7 +11634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="19.5">
       <c r="A97" s="10">
         <v>10</v>
       </c>
@@ -11691,7 +11703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="19.5">
       <c r="A98" s="10">
         <v>10</v>
       </c>
@@ -13533,190 +13545,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12" name="Textbooks"/>
-    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13" name="LAS"/>
+    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 D73:F81 H73:I81 D83:F91 H83:I91 D93:F101 H93:I101 Q99:R101 W99:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K99:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 K63:L71 K73:K81 K83:K91 K93:K98 L72:L98 Q63:R71 Q73:Q81 Q83:Q91 Q93:Q98 R72:R98 W63:W71 W73:W81 W83:W91 W93:W98 X63:X98" name="LAS"/>
     <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
@@ -13726,15 +13558,18 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 R99:R101 X112:X127 X53:X61 L112:L127 F43:F51 F33:F41 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 F103:F110 F14:F21 L53:L61 R112:R127 R103:R110 L103:L110 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 L99:L101 F5:F12 R53:R61 F112:F127 F53:F61 X103:X110 R14:R21 R5:R12 F23:F31" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
       <formula1>"2024,2025"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F63:F71 F73:F81 F83:F91 F93:F101 L63:L98 R63:R98 X63:X98 X99:X101" xr:uid="{06F92621-2940-4C98-9C07-47DA4C406BDE}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13749,7 +13584,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -17903,7 +17738,7 @@
       </c>
     </row>
     <row r="66" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="67" spans="1:27" ht="19.5">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -17972,7 +17807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="19.5">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -18041,7 +17876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="19.5">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -18110,7 +17945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="19.5">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -18179,7 +18014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="38.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -18248,7 +18083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="19.149999999999999">
+    <row r="72" spans="1:27" ht="19.5">
       <c r="A72" s="10">
         <v>7</v>
       </c>
@@ -18317,7 +18152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="19.5">
       <c r="A73" s="38">
         <v>7</v>
       </c>
@@ -18386,7 +18221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="19.5">
       <c r="A74" s="10">
         <v>7</v>
       </c>
@@ -18455,7 +18290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="19.5">
       <c r="A75" s="10">
         <v>7</v>
       </c>
@@ -18524,7 +18359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="19.5">
       <c r="A76" s="38">
         <v>7</v>
       </c>
@@ -18593,7 +18428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="19.5">
       <c r="A77" s="10">
         <v>7</v>
       </c>
@@ -18662,8 +18497,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" s="7" customFormat="1"/>
+    <row r="79" spans="1:27" ht="19.5">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -18732,7 +18567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="19.5">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -18801,7 +18636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="19.5">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -18870,7 +18705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="19.149999999999999">
+    <row r="82" spans="1:27" ht="19.5">
       <c r="A82" s="10">
         <v>8</v>
       </c>
@@ -18939,7 +18774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="19.5">
       <c r="A83" s="10">
         <v>8</v>
       </c>
@@ -19008,7 +18843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="19.5">
       <c r="A84" s="10">
         <v>8</v>
       </c>
@@ -19077,7 +18912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="19.5">
       <c r="A85" s="38">
         <v>8</v>
       </c>
@@ -19146,7 +18981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="19.5">
       <c r="A86" s="10">
         <v>8</v>
       </c>
@@ -19215,7 +19050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="19.5">
       <c r="A87" s="10">
         <v>8</v>
       </c>
@@ -19284,7 +19119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="19.5">
       <c r="A88" s="38">
         <v>8</v>
       </c>
@@ -19353,7 +19188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="19.5">
       <c r="A89" s="10">
         <v>8</v>
       </c>
@@ -19422,8 +19257,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="90" spans="1:27" s="7" customFormat="1"/>
+    <row r="91" spans="1:27" ht="19.5">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -19492,7 +19327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="19.149999999999999">
+    <row r="92" spans="1:27" ht="19.5">
       <c r="A92" s="10">
         <v>9</v>
       </c>
@@ -19561,7 +19396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="19.5">
       <c r="A93" s="10">
         <v>9</v>
       </c>
@@ -19630,7 +19465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="19.5">
       <c r="A94" s="10">
         <v>9</v>
       </c>
@@ -19699,7 +19534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="19.5">
       <c r="A95" s="10">
         <v>9</v>
       </c>
@@ -19768,7 +19603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="19.5">
       <c r="A96" s="10">
         <v>9</v>
       </c>
@@ -19837,7 +19672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="19.5">
       <c r="A97" s="38">
         <v>9</v>
       </c>
@@ -19906,7 +19741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="19.5">
       <c r="A98" s="10">
         <v>9</v>
       </c>
@@ -19975,7 +19810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="19.5">
       <c r="A99" s="10">
         <v>9</v>
       </c>
@@ -20044,7 +19879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="19.5">
       <c r="A100" s="38">
         <v>9</v>
       </c>
@@ -20113,7 +19948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="19.5">
       <c r="A101" s="10">
         <v>9</v>
       </c>
@@ -20182,8 +20017,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="103" spans="1:27" ht="19.149999999999999">
+    <row r="102" spans="1:27" s="7" customFormat="1"/>
+    <row r="103" spans="1:27" ht="19.5">
       <c r="A103" s="10">
         <v>10</v>
       </c>
@@ -20252,7 +20087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="19.5">
       <c r="A104" s="10">
         <v>10</v>
       </c>
@@ -20321,7 +20156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="19.5">
       <c r="A105" s="10">
         <v>10</v>
       </c>
@@ -20390,7 +20225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="19.5">
       <c r="A106" s="10">
         <v>10</v>
       </c>
@@ -20459,7 +20294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="19.149999999999999">
+    <row r="107" spans="1:27" ht="19.5">
       <c r="A107" s="10">
         <v>10</v>
       </c>
@@ -20528,7 +20363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="19.5">
       <c r="A108" s="10">
         <v>10</v>
       </c>
@@ -20597,7 +20432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="19.149999999999999">
+    <row r="109" spans="1:27" ht="19.5">
       <c r="A109" s="38">
         <v>10</v>
       </c>
@@ -20666,7 +20501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="19.149999999999999">
+    <row r="110" spans="1:27" ht="19.5">
       <c r="A110" s="10">
         <v>10</v>
       </c>
@@ -20735,7 +20570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="19.149999999999999">
+    <row r="111" spans="1:27" ht="19.5">
       <c r="A111" s="10">
         <v>10</v>
       </c>
@@ -20804,7 +20639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="19.5">
       <c r="A112" s="38">
         <v>10</v>
       </c>
@@ -20873,7 +20708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="19.149999999999999">
+    <row r="113" spans="1:28" ht="19.5">
       <c r="A113" s="10">
         <v>10</v>
       </c>
@@ -22006,190 +21841,10 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
-    <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D91:F101 D115:F122 P2:R10 N3:O10 V2:X10 T3:U10 N12:R19 T12:X19 H3:L10 Z3:AA10 Z12:AA19 H12:L19 N21:R29 T21:X29 Z21:AA29 H21:L29 T31:X41 Z31:AA41 H31:L41 T43:X53 Z43:AA53 H43:L53 T55:X65 Z55:AA65 H55:L65 T67:X77 Z67:AA77 H67:L77 T79:X89 Z79:AA89 H79:L89 T91:X101 Z91:AA101 H91:L101 T103:X113 Z103:AA113 H103:L113 N115:R122 T115:X122 Z115:AA122 H115:L122 D103:F113 N31:R41 N43:R53 N55:R65 N67:R77 N79:R89 N91:R101 N103:R113" name="LAS"/>
+    <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D91:F101 D115:F122 P2:R10 N3:O10 V2:X10 T3:U10 N12:R19 T12:X19 H3:L10 Z3:AA10 Z12:AA19 H12:L19 N21:R29 T21:X29 Z21:AA29 H21:L29 T31:X41 Z31:AA41 H31:L41 T43:X53 Z43:AA53 H43:L53 T55:X65 Z55:AA65 H55:L65 Z67:AA77 Z79:AA89 Z91:AA101 Z103:AA113 N115:R122 T115:X122 Z115:AA122 H115:L122 D103:F113 N31:R41 N43:R53 N55:R65 H67:L77 H79:L89 H91:L101 H103:L113 N67:R77 N79:R89 N91:R101 N103:R113 T67:X77 T79:X89 T91:X101 T103:X113" name="LAS"/>
     <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 G3:G10 M3:M10 S3:S10 Y3:Y10 Y12:Y19 G12:G19 M12:M19 S12:S19 Y21:Y29 G21:G29 M21:M29 S21:S29 Y31:Y41 G31:G41 M31:M41 S31:S41 Y43:Y53 G43:G53 M43:M53 S43:S53 Y55:Y65 G55:G65 M55:M65 S55:S65 Y67:Y77 G67:G77 M67:M77 S67:S77 Y79:Y89 G79:G89 M79:M89 S79:S89 Y91:Y101 G91:G101 M91:M101 S91:S101 Y103:Y113 G103:G113 M103:M113 S103:S113 Y115:Y122 G115:G122 M115:M122 S115:S122" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
@@ -22199,12 +21854,15 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 R12:R19 R3:R10 X55:X65 F21:F29 F31:F41 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 F3:F10 R115:R122 L55:L65 X115:X122 F12:F19 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 F43:F53 F115:F122 R55:R65 L115:L122 F55:F65" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
       <formula1>"2024,2025"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F67:F77 F79:F89 F91:F101 F103:F113 L67:L77 L79:L89 L91:L101 L103:L113 R67:R77 R79:R89 R91:R101 R103:R113 X67:X77 X79:X89 X91:X101 X103:X113" xr:uid="{E8ECA91D-3287-45F3-AF58-46273BC6B759}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
